--- a/KIT-REPRISE/05-analyses-accident.xlsx
+++ b/KIT-REPRISE/05-analyses-accident.xlsx
@@ -5,9 +5,15 @@
   <sheets>
     <sheet name="Analyses" sheetId="1" r:id="rId1"/>
     <sheet name="Actions" sheetId="2" r:id="rId2"/>
-    <sheet name="Exemple Analyses" sheetId="3" r:id="rId3"/>
-    <sheet name="Exemple Actions" sheetId="4" r:id="rId4"/>
-    <sheet name="Consignes" sheetId="5" r:id="rId5"/>
+    <sheet name="Faits" sheetId="3" r:id="rId3"/>
+    <sheet name="Pourquoi" sheetId="4" r:id="rId4"/>
+    <sheet name="Ishikawa" sheetId="5" r:id="rId5"/>
+    <sheet name="Exemple Analyses" sheetId="6" r:id="rId6"/>
+    <sheet name="Exemple Actions" sheetId="7" r:id="rId7"/>
+    <sheet name="Exemple Faits" sheetId="8" r:id="rId8"/>
+    <sheet name="Exemple Pourquoi" sheetId="9" r:id="rId9"/>
+    <sheet name="Exemple Ishikawa" sheetId="10" r:id="rId10"/>
+    <sheet name="Consignes" sheetId="11" r:id="rId11"/>
   </sheets>
 </workbook>
 </file>
@@ -444,9 +450,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:D4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -456,218 +462,64 @@
         <v>Agent</v>
       </c>
       <c r="C1" t="str">
-        <v>Action</v>
+        <v>Catégorie</v>
       </c>
       <c r="D1" t="str">
-        <v>Responsable</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Échéance</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Statut</v>
+        <v>Cause</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>dtst-atmp-1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Dubreuil Antoine</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Matériel</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Toiture non entretenue</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>dtst-atmp-1</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Dubreuil Antoine</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Méthode</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Pas de consigne de signalement des fuites</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>dtst-atmp-1</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Dubreuil Antoine</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Milieu</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Entrée sans tapis</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D4"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J4"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>ID AT/MP</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Nom</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Prénom</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Date AT</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Service</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Méthode</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Statut</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Conclusion</v>
-      </c>
-      <c r="I1" t="str">
-        <v>Date analyse</v>
-      </c>
-      <c r="J1" t="str">
-        <v>Auteur</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>dtst-atmp-1</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Dubreuil</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Antoine</v>
-      </c>
-      <c r="D2" t="str">
-        <v>2025-03-17</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Espaces Verts &amp; Paysage</v>
-      </c>
-      <c r="F2" t="str">
-        <v>5 Pourquoi</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Faite</v>
-      </c>
-      <c r="H2" t="str">
-        <v>Fuite de toiture non signalée au service Patrimoine</v>
-      </c>
-      <c r="I2" t="str">
-        <v>2026-09-10</v>
-      </c>
-      <c r="J2" t="str">
-        <v>RH1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>dtst-atmp-2</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Faucher</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Julien</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2025-04-01</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Atelier Mécanique</v>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v>En attente</v>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v/>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>dtst-atmp-3</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Girard</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Camille</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2025-04-17</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Propreté de la Ville</v>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v>En attente</v>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v/>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J4"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>ID AT/MP</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Agent</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Action</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Responsable</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Échéance</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Statut</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>dtst-atmp-1</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Dubreuil Antoine</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Poser un tapis antidérapant à l'entrée</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Chef d'équipe</v>
-      </c>
-      <c r="E2" t="str">
-        <v>2026-10-15</v>
-      </c>
-      <c r="F2" t="str">
-        <v>En cours</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F2"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F33"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="28.83203125" customWidth="1"/>
@@ -1017,9 +869,802 @@
         <v>texte libre</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Faits</v>
+      </c>
+      <c r="B18" t="str">
+        <v>ID AT/MP</v>
+      </c>
+      <c r="C18" t="str">
+        <v>non</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Identifiant</v>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v>facultatif : laissez vide pour une nouvelle ligne (rattachement par « Nom » + « Date AT »)</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Faits</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Agent</v>
+      </c>
+      <c r="C19" t="str">
+        <v>non</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Texte</v>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <v>non lue à l'import : l'application la calcule ou la reprend d'un enregistrement rattaché</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Faits</v>
+      </c>
+      <c r="B20" t="str">
+        <v>N°</v>
+      </c>
+      <c r="C20" t="str">
+        <v>non</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Nombre</v>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>Faits</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Date</v>
+      </c>
+      <c r="C21" t="str">
+        <v>non</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Date AAAA-MM-JJ (une date Excel convient aussi)</v>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>Faits</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Fait</v>
+      </c>
+      <c r="C22" t="str">
+        <v>OUI</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Texte</v>
+      </c>
+      <c r="E22" t="str">
+        <v/>
+      </c>
+      <c r="F22" t="str">
+        <v>texte libre</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>Faits</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Type</v>
+      </c>
+      <c r="C23" t="str">
+        <v>non</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Texte</v>
+      </c>
+      <c r="E23" t="str">
+        <v>Fait · Opinion</v>
+      </c>
+      <c r="F23" t="str">
+        <v>liste : une valeur inconnue est remplacée par « Fait »</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>Faits</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Découle du fait n°</v>
+      </c>
+      <c r="C24" t="str">
+        <v>non</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Nombre</v>
+      </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
+      <c r="F24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>Pourquoi</v>
+      </c>
+      <c r="B25" t="str">
+        <v>ID AT/MP</v>
+      </c>
+      <c r="C25" t="str">
+        <v>non</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Identifiant</v>
+      </c>
+      <c r="E25" t="str">
+        <v/>
+      </c>
+      <c r="F25" t="str">
+        <v>facultatif : laissez vide pour une nouvelle ligne (rattachement par « Nom » + « Date AT »)</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>Pourquoi</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Agent</v>
+      </c>
+      <c r="C26" t="str">
+        <v>non</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Texte</v>
+      </c>
+      <c r="E26" t="str">
+        <v/>
+      </c>
+      <c r="F26" t="str">
+        <v>non lue à l'import : l'application la calcule ou la reprend d'un enregistrement rattaché</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>Pourquoi</v>
+      </c>
+      <c r="B27" t="str">
+        <v>N°</v>
+      </c>
+      <c r="C27" t="str">
+        <v>non</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Nombre</v>
+      </c>
+      <c r="E27" t="str">
+        <v/>
+      </c>
+      <c r="F27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>Pourquoi</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Question</v>
+      </c>
+      <c r="C28" t="str">
+        <v>non</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Texte</v>
+      </c>
+      <c r="E28" t="str">
+        <v/>
+      </c>
+      <c r="F28" t="str">
+        <v>texte libre</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>Pourquoi</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Réponse</v>
+      </c>
+      <c r="C29" t="str">
+        <v>non</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Texte</v>
+      </c>
+      <c r="E29" t="str">
+        <v/>
+      </c>
+      <c r="F29" t="str">
+        <v>texte libre</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>Ishikawa</v>
+      </c>
+      <c r="B30" t="str">
+        <v>ID AT/MP</v>
+      </c>
+      <c r="C30" t="str">
+        <v>non</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Identifiant</v>
+      </c>
+      <c r="E30" t="str">
+        <v/>
+      </c>
+      <c r="F30" t="str">
+        <v>facultatif : laissez vide pour une nouvelle ligne (rattachement par « Nom » + « Date AT »)</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>Ishikawa</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Agent</v>
+      </c>
+      <c r="C31" t="str">
+        <v>non</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Texte</v>
+      </c>
+      <c r="E31" t="str">
+        <v/>
+      </c>
+      <c r="F31" t="str">
+        <v>non lue à l'import : l'application la calcule ou la reprend d'un enregistrement rattaché</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>Ishikawa</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Catégorie</v>
+      </c>
+      <c r="C32" t="str">
+        <v>OUI</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Texte</v>
+      </c>
+      <c r="E32" t="str">
+        <v>Matériel · Méthode · Milieu</v>
+      </c>
+      <c r="F32" t="str">
+        <v>liste fermée : une valeur inconnue fait refuser la ligne</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>Ishikawa</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Cause</v>
+      </c>
+      <c r="C33" t="str">
+        <v>OUI</v>
+      </c>
+      <c r="D33" t="str">
+        <v>Texte</v>
+      </c>
+      <c r="E33" t="str">
+        <v/>
+      </c>
+      <c r="F33" t="str">
+        <v>texte libre</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F17"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F33"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F1"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>ID AT/MP</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Agent</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Action</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Responsable</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Échéance</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Statut</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G1"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>ID AT/MP</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Agent</v>
+      </c>
+      <c r="C1" t="str">
+        <v>N°</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Date</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Fait</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Type</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Découle du fait n°</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:G1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E1"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>ID AT/MP</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Agent</v>
+      </c>
+      <c r="C1" t="str">
+        <v>N°</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Question</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Réponse</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:E1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D1"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>ID AT/MP</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Agent</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Catégorie</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Cause</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:D1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>ID AT/MP</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Nom</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Prénom</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Date AT</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Service</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Méthode</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Statut</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Conclusion</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Date analyse</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Auteur</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>dtst-atmp-1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Dubreuil</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Antoine</v>
+      </c>
+      <c r="D2" t="str">
+        <v>2025-03-17</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Espaces Verts &amp; Paysage</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Arbre des causes</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Faite</v>
+      </c>
+      <c r="H2" t="str">
+        <v>Fuite de toiture non signalée au service Patrimoine</v>
+      </c>
+      <c r="I2" t="str">
+        <v>2026-09-10</v>
+      </c>
+      <c r="J2" t="str">
+        <v>RH1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>dtst-atmp-2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Faucher</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Julien</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2025-04-01</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Atelier Mécanique</v>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v>En attente</v>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v/>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>dtst-atmp-3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Girard</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Camille</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2025-04-17</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Propreté de la Ville</v>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v>En attente</v>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v/>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:J4"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F2"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>ID AT/MP</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Agent</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Action</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Responsable</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Échéance</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Statut</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>dtst-atmp-1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Dubreuil Antoine</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Poser un tapis antidérapant à l'entrée</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Chef d'équipe</v>
+      </c>
+      <c r="E2" t="str">
+        <v>2026-10-15</v>
+      </c>
+      <c r="F2" t="str">
+        <v>En cours</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F2"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>ID AT/MP</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Agent</v>
+      </c>
+      <c r="C1" t="str">
+        <v>N°</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Date</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Fait</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Type</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Découle du fait n°</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>dtst-atmp-1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Dubreuil Antoine</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Fuite de toiture au-dessus de l'entrée</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Fait</v>
+      </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>dtst-atmp-1</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Dubreuil Antoine</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-03-02</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Flaque sur le sol de l'entrée</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Fait</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>dtst-atmp-1</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Dubreuil Antoine</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-03-02</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Personne ne pensait devoir signaler la fuite</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Opinion</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:G4"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E3"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>ID AT/MP</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Agent</v>
+      </c>
+      <c r="C1" t="str">
+        <v>N°</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Question</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Réponse</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>dtst-atmp-1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Dubreuil Antoine</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Pourquoi l'agent a-t-il glissé ?</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Le sol était mouillé</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>dtst-atmp-1</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Dubreuil Antoine</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Pourquoi le sol était-il mouillé ?</v>
+      </c>
+      <c r="E3" t="str">
+        <v>La fuite de toiture n'avait pas été signalée</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:E3"/>
   </ignoredErrors>
 </worksheet>
 </file>